--- a/doc/docs/EAP_PRODUCAO.xlsx
+++ b/doc/docs/EAP_PRODUCAO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\github_corrigido_dashboard_obrasRev1\github\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2299176A-C19C-40BD-A1D5-6456718FD83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C358BF-8DF4-4D62-BADE-D5393D7E8BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EAP_PRODUCAO" sheetId="2" r:id="rId1"/>
@@ -953,7 +953,7 @@
         <v>2426.84</v>
       </c>
       <c r="E16" s="2">
-        <v>1747.73</v>
+        <v>1538.59</v>
       </c>
       <c r="F16">
         <v>2735</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>679.11000000000013</v>
+        <v>888.25000000000023</v>
       </c>
       <c r="J16" s="5"/>
     </row>
@@ -1109,19 +1109,19 @@
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P27">
         <f>SUM(E3:E16)</f>
-        <v>15619.635000000002</v>
+        <v>15410.495000000003</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P28">
         <f>14468.56-P27</f>
-        <v>-1151.0750000000025</v>
+        <v>-941.93500000000313</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P29">
         <f>P28+2135.09</f>
-        <v>984.0149999999976</v>
+        <v>1193.154999999997</v>
       </c>
     </row>
     <row r="34" spans="8:8" x14ac:dyDescent="0.3">

--- a/doc/docs/EAP_PRODUCAO.xlsx
+++ b/doc/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C358BF-8DF4-4D62-BADE-D5393D7E8BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA540C8-E5A2-40B7-9983-66D5BB8B77CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -953,7 +953,7 @@
         <v>2426.84</v>
       </c>
       <c r="E16" s="2">
-        <v>1538.59</v>
+        <v>1460.1</v>
       </c>
       <c r="F16">
         <v>2735</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>888.25000000000023</v>
+        <v>966.74000000000024</v>
       </c>
       <c r="J16" s="5"/>
     </row>
@@ -1109,19 +1109,19 @@
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P27">
         <f>SUM(E3:E16)</f>
-        <v>15410.495000000003</v>
+        <v>15332.005000000003</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P28">
         <f>14468.56-P27</f>
-        <v>-941.93500000000313</v>
+        <v>-863.44500000000335</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P29">
         <f>P28+2135.09</f>
-        <v>1193.154999999997</v>
+        <v>1271.6449999999968</v>
       </c>
     </row>
     <row r="34" spans="8:8" x14ac:dyDescent="0.3">

--- a/doc/docs/EAP_PRODUCAO.xlsx
+++ b/doc/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA540C8-E5A2-40B7-9983-66D5BB8B77CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084374D7-219F-4865-A67B-DF058096A9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -722,7 +722,7 @@
         <v>584</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I16" si="0">D7-E7</f>
+        <f t="shared" ref="I7:I17" si="0">D7-E7</f>
         <v>-473.39499999999998</v>
       </c>
       <c r="J7" s="5"/>
@@ -977,11 +977,18 @@
       <c r="D17" s="3">
         <v>2545.85</v>
       </c>
+      <c r="E17" s="2">
+        <v>78.19</v>
+      </c>
       <c r="F17">
         <v>2361</v>
       </c>
       <c r="G17">
         <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>2467.66</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/doc/docs/EAP_PRODUCAO.xlsx
+++ b/doc/docs/EAP_PRODUCAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084374D7-219F-4865-A67B-DF058096A9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD6A140-D5A1-4F1F-B02B-0CAC26B11EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EAP_PRODUCAO" sheetId="2" r:id="rId1"/>
@@ -959,7 +959,7 @@
         <v>2735</v>
       </c>
       <c r="G16">
-        <v>5747</v>
+        <v>5246</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
@@ -978,7 +978,7 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <v>78.19</v>
+        <v>378.57</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>2467.66</v>
+        <v>2167.2799999999997</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/doc/docs/EAP_PRODUCAO.xlsx
+++ b/doc/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD6A140-D5A1-4F1F-B02B-0CAC26B11EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224A9EBC-ABC2-4488-9D98-6530CCAF7884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -978,7 +978,7 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <v>378.57</v>
+        <v>487.87</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>2167.2799999999997</v>
+        <v>2057.98</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
